--- a/data/trans_dic/P70D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,47</t>
+          <t>4,93; 15,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 36,29</t>
+          <t>11,98; 37,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 21,73</t>
+          <t>9,09; 21,56</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,71</t>
+          <t>1,89; 4,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,5</t>
+          <t>3,58; 6,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,01</t>
+          <t>2,73; 5,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,71</t>
+          <t>2,27; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,1</t>
+          <t>3,24; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,99</t>
+          <t>3,18; 6,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,01</t>
+          <t>2,54; 5,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,33</t>
+          <t>4,47; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,63</t>
+          <t>3,61; 5,52</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6924; 18928</t>
+          <t>6449; 19929</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9089; 28953</t>
+          <t>9555; 30169</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18498; 45748</t>
+          <t>19137; 45405</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24774; 65145</t>
+          <t>26182; 64263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33887; 61408</t>
+          <t>33860; 61122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64323; 116580</t>
+          <t>63527; 119101</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9453; 30234</t>
+          <t>10207; 30034</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13993; 31107</t>
+          <t>14218; 28992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27358; 53209</t>
+          <t>28247; 53395</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50563; 98440</t>
+          <t>49866; 98960</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65734; 107325</t>
+          <t>65424; 106449</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122967; 193078</t>
+          <t>123810; 189197</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 15,24</t>
+          <t>4,9; 14,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 37,81</t>
+          <t>9,99; 23,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 21,56</t>
+          <t>7,76; 15,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,65</t>
+          <t>2,98; 5,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,47</t>
+          <t>4,43; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,12</t>
+          <t>3,84; 5,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,67</t>
+          <t>2,0; 6,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,61</t>
+          <t>3,23; 6,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,01</t>
+          <t>3,08; 5,92</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,04</t>
+          <t>3,38; 5,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,27</t>
+          <t>4,95; 7,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,52</t>
+          <t>4,27; 5,69</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27993</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6449; 19929</t>
+          <t>7958; 22750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9555; 30169</t>
+          <t>8693; 20432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19137; 45405</t>
+          <t>19348; 37970</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>103693</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26182; 64263</t>
+          <t>37945; 65551</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33860; 61122</t>
+          <t>41940; 67642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63527; 119101</t>
+          <t>85225; 126158</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>41073</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10207; 30034</t>
+          <t>9834; 32327</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14218; 28992</t>
+          <t>15528; 32389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28247; 53395</t>
+          <t>29960; 57576</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49866; 98960</t>
+          <t>65108; 101650</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65424; 106449</t>
+          <t>75024; 107392</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123810; 189197</t>
+          <t>146873; 195659</t>
         </is>
       </c>
     </row>
